--- a/report_2408.xlsx
+++ b/report_2408.xlsx
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="B25" s="89" t="n">
-        <v>7.2</v>
+        <v>7.16</v>
       </c>
       <c r="C25" s="89" t="n">
         <v>7.25</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>-0.64</v>
+        <v>-1.21</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.32</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>-1.19</v>
+        <v>-1.76</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>-0.62</v>
@@ -8682,9 +8682,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="95" t="inlineStr">
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>5.13</v>
+        <v>3.06</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>5.13</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>8.98</v>
+        <v>6.37</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>8.98</v>
@@ -9028,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>35.7</v>
+        <v>14.25</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>35.7</v>
@@ -9125,13 +9125,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>35.7</v>
+        <v>14.25</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>35.7</v>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>3.85</v>
+        <v>2.19</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>3.85</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>4.19</v>
+        <v>2.76</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>4.19</v>
@@ -9573,13 +9573,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="inlineStr">
+      <c r="A30" s="97" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>35.19</v>
+        <v>17.33</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>35.19</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>45.13</v>
+        <v>29.31</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>45.13</v>
@@ -9772,9 +9772,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C32" s="95" t="inlineStr">
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>5.17</v>
+        <v>2.72</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>5.17</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>8.869999999999999</v>
+        <v>4.91</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>8.869999999999999</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>33.44</v>
+        <v>15.44</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>33.44</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>33.44</v>
+        <v>15.44</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>33.44</v>
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="B38" s="96" t="n">
-        <v>-4.9</v>
+        <v>-5.66</v>
       </c>
       <c r="C38" s="96" t="n">
         <v>-0.2</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="B39" s="96" t="n">
-        <v>0.24</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C39" s="96" t="n">
         <v>5.44</v>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>18.74</v>
+        <v>17.53</v>
       </c>
       <c r="C40" s="96" t="n">
         <v>34.53</v>
@@ -10766,7 +10766,7 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>24.2</v>
+        <v>23.06</v>
       </c>
       <c r="C41" s="96" t="n">
         <v>35.82</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>10.4</v>
+        <v>10.23</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>11.37</v>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>12.41</v>
+        <v>12.24</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>13.41</v>
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>53.23</v>
+        <v>50.72</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>76.56</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>61.63</v>
+        <v>60.46</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>69.98</v>
@@ -11952,168 +11952,168 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="95" t="inlineStr">
+      <c r="B52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C52" s="95" t="inlineStr">
+      <c r="E52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D52" s="95" t="inlineStr">
+      <c r="F52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E52" s="95" t="inlineStr">
+      <c r="H52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F52" s="93" t="inlineStr">
+      <c r="K52" s="94" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G52" s="95" t="inlineStr">
+      <c r="M52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O52" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="93" t="inlineStr">
+      <c r="Q52" s="94" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R52" s="94" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I52" s="93" t="inlineStr">
+      <c r="T52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J52" s="95" t="inlineStr">
+      <c r="U52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K52" s="94" t="inlineStr">
+      <c r="V52" s="94" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L52" s="93" t="inlineStr">
+      <c r="W52" s="94" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="X52" s="94" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y52" s="95" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z52" s="95" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M52" s="93" t="inlineStr">
+      <c r="AB52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N52" s="93" t="inlineStr">
+      <c r="AC52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P52" s="95" t="inlineStr">
+      <c r="AD52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q52" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R52" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U52" s="95" t="inlineStr">
+      <c r="AE52" s="95" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V52" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W52" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="X52" s="94" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y52" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z52" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC52" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD52" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE52" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="78" t="inlineStr">
+      <c r="A53" s="97" t="inlineStr">
         <is>
           <t>fr40:RNG60</t>
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-7.38</v>
+        <v>-11.77</v>
       </c>
       <c r="C53" s="96" t="n">
-        <v>-7.38</v>
+        <v>-9.98</v>
       </c>
       <c r="D53" s="96" t="n">
         <v>-7.38</v>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>-1.52</v>
+        <v>-4.9</v>
       </c>
       <c r="C54" s="96" t="n">
-        <v>-1.52</v>
+        <v>-4.15</v>
       </c>
       <c r="D54" s="96" t="n">
         <v>-1.52</v>
@@ -12298,16 +12298,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="78" t="inlineStr">
+      <c r="A55" s="97" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>62.29</v>
+        <v>16.12</v>
       </c>
       <c r="C55" s="96" t="n">
-        <v>62.29</v>
+        <v>26.39</v>
       </c>
       <c r="D55" s="96" t="n">
         <v>62.29</v>
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>52.9</v>
+        <v>23.33</v>
       </c>
       <c r="C56" s="96" t="n">
-        <v>52.9</v>
+        <v>31.87</v>
       </c>
       <c r="D56" s="96" t="n">
         <v>52.9</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-3.23</v>
+        <v>-5.92</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-3.23</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>6.14</v>
+        <v>4.62</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>6.14</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>28.05</v>
+        <v>16.13</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>28.05</v>
@@ -12858,7 +12858,7 @@
         <v>63.6</v>
       </c>
       <c r="E60" s="96" t="n">
-        <v>53.47</v>
+        <v>53.48</v>
       </c>
       <c r="F60" s="96" t="n">
         <v>42.29</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>33.81</v>
+        <v>22.58</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>33.81</v>
@@ -13039,7 +13039,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-13.77&lt;=-10;ixic:RSI2:33.44&lt;=36;ixic:RSI2:33.44&lt;=35;jp225:RSI9:24.2&lt;=28</t>
+          <t>今日买报：cy:RNG60:-13.77&lt;=-10;us500:RSI2:14.25&lt;=28;us500:RSI2:14.25&lt;=22;us30:RSI3:17.33&lt;=25;ixic:RSI2:15.44&lt;=36;ixic:RSI2:15.44&lt;=35;jp225:RSI9:23.06&lt;=28;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
         </is>
       </c>
     </row>

--- a/report_2408.xlsx
+++ b/report_2408.xlsx
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="B25" s="90" t="n">
-        <v>7.11</v>
+        <v>7.14</v>
       </c>
       <c r="C25" s="90" t="n">
         <v>7.16</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="91" t="n">
-        <v>-0.77</v>
+        <v>-0.22</v>
       </c>
       <c r="C26" s="91" t="n">
         <v>-1.21</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="91" t="n">
-        <v>-2.47</v>
+        <v>-1.94</v>
       </c>
       <c r="C27" s="91" t="n">
         <v>-1.76</v>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="97" t="n">
-        <v>3.06</v>
+        <v>-0.03</v>
       </c>
       <c r="C23" s="97" t="n">
         <v>3.06</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="97" t="n">
-        <v>6.37</v>
+        <v>3.28</v>
       </c>
       <c r="C24" s="97" t="n">
         <v>6.37</v>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="B25" s="97" t="n">
-        <v>14.25</v>
+        <v>4.87</v>
       </c>
       <c r="C25" s="97" t="n">
         <v>14.25</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B26" s="97" t="n">
-        <v>14.25</v>
+        <v>4.87</v>
       </c>
       <c r="C26" s="97" t="n">
         <v>14.25</v>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="97" t="n">
-        <v>2.19</v>
+        <v>-0.9</v>
       </c>
       <c r="C28" s="97" t="n">
         <v>2.19</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="97" t="n">
-        <v>2.76</v>
+        <v>-0.24</v>
       </c>
       <c r="C29" s="97" t="n">
         <v>2.76</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="97" t="n">
-        <v>17.33</v>
+        <v>7.57</v>
       </c>
       <c r="C30" s="97" t="n">
         <v>17.33</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="97" t="n">
-        <v>29.31</v>
+        <v>16.82</v>
       </c>
       <c r="C31" s="97" t="n">
         <v>29.31</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="97" t="n">
-        <v>2.72</v>
+        <v>-0.63</v>
       </c>
       <c r="C33" s="97" t="n">
         <v>2.72</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="97" t="n">
-        <v>4.91</v>
+        <v>1.62</v>
       </c>
       <c r="C34" s="97" t="n">
         <v>4.91</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B35" s="97" t="n">
-        <v>15.44</v>
+        <v>6.21</v>
       </c>
       <c r="C35" s="97" t="n">
         <v>15.44</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="97" t="n">
-        <v>15.44</v>
+        <v>6.21</v>
       </c>
       <c r="C36" s="97" t="n">
         <v>15.44</v>
@@ -10469,16 +10469,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="78" t="inlineStr">
+      <c r="A38" s="87" t="inlineStr">
         <is>
           <t>jp225:RNG60</t>
         </is>
       </c>
       <c r="B38" s="97" t="n">
-        <v>-5.66</v>
+        <v>-18.71</v>
       </c>
       <c r="C38" s="97" t="n">
-        <v>-5.66</v>
+        <v>-5.68</v>
       </c>
       <c r="D38" s="97" t="n">
         <v>-0.2</v>
@@ -10572,10 +10572,10 @@
         </is>
       </c>
       <c r="B39" s="97" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-15.69</v>
       </c>
       <c r="C39" s="97" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="D39" s="97" t="n">
         <v>5.44</v>
@@ -10663,16 +10663,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="inlineStr">
+      <c r="A40" s="87" t="inlineStr">
         <is>
           <t>jp225:RSI5</t>
         </is>
       </c>
       <c r="B40" s="97" t="n">
-        <v>17.53</v>
+        <v>7.46</v>
       </c>
       <c r="C40" s="97" t="n">
-        <v>17.53</v>
+        <v>17.5</v>
       </c>
       <c r="D40" s="97" t="n">
         <v>34.53</v>
@@ -10766,10 +10766,10 @@
         </is>
       </c>
       <c r="B41" s="97" t="n">
-        <v>23.06</v>
+        <v>12.28</v>
       </c>
       <c r="C41" s="97" t="n">
-        <v>23.06</v>
+        <v>23.03</v>
       </c>
       <c r="D41" s="97" t="n">
         <v>35.82</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B48" s="97" t="n">
-        <v>8.949999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C48" s="97" t="n">
         <v>10.23</v>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="B49" s="97" t="n">
-        <v>10.44</v>
+        <v>10.26</v>
       </c>
       <c r="C49" s="97" t="n">
         <v>12.24</v>
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="B50" s="97" t="n">
-        <v>26.24</v>
+        <v>25.51</v>
       </c>
       <c r="C50" s="97" t="n">
         <v>50.72</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="B51" s="97" t="n">
-        <v>45.03</v>
+        <v>44.37</v>
       </c>
       <c r="C51" s="97" t="n">
         <v>60.46</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="97" t="n">
-        <v>-5.92</v>
+        <v>-7.49</v>
       </c>
       <c r="C58" s="97" t="n">
         <v>-5.92</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="97" t="n">
-        <v>4.62</v>
+        <v>2.32</v>
       </c>
       <c r="C59" s="97" t="n">
         <v>4.62</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="97" t="n">
-        <v>16.13</v>
+        <v>11.26</v>
       </c>
       <c r="C60" s="97" t="n">
         <v>16.13</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="97" t="n">
-        <v>22.58</v>
+        <v>17.31</v>
       </c>
       <c r="C61" s="97" t="n">
         <v>22.58</v>
@@ -13039,7 +13039,7 @@
     <row r="63">
       <c r="A63" s="93" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-14.42&lt;=-10;hk50:RSI6:28.51&lt;=30;us500:RSI2:14.25&lt;=28;us500:RSI2:14.25&lt;=22;us30:RSI3:17.33&lt;=25;ixic:RSI2:15.44&lt;=36;ixic:RSI2:15.44&lt;=35;jp225:RSI9:23.06&lt;=28;vn:RSI3:14.12&lt;=25;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
+          <t>今日买报：cy:RNG60:-14.42&lt;=-10;hk50:RSI6:28.51&lt;=30;us500:RSI2:4.87&lt;=28;us500:RSI2:4.87&lt;=22;us30:RSI3:7.57&lt;=25;ixic:RSI2:6.21&lt;=36;ixic:RSI2:6.21&lt;=35;jp225:RNG60:-18.71&lt;=-10;jp225:RSI5:7.46&lt;=15;jp225:RSI9:12.28&lt;=28;vn:RSI3:14.12&lt;=25;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
         </is>
       </c>
     </row>

--- a/report_2408.xlsx
+++ b/report_2408.xlsx
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B25" s="91" t="n">
-        <v>7.15</v>
+        <v>7.16</v>
       </c>
       <c r="C25" s="91" t="n">
         <v>7.15</v>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="B26" s="92" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="C26" s="92" t="n">
         <v>-0.21</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B27" s="92" t="n">
-        <v>-1.92</v>
+        <v>-1.81</v>
       </c>
       <c r="C27" s="92" t="n">
         <v>-1.93</v>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="B23" s="98" t="n">
-        <v>-0.03</v>
+        <v>0.5</v>
       </c>
       <c r="C23" s="98" t="n">
         <v>-0.03</v>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="B24" s="98" t="n">
-        <v>3.28</v>
+        <v>5.79</v>
       </c>
       <c r="C24" s="98" t="n">
         <v>3.28</v>
@@ -9037,13 +9037,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="98" t="n">
-        <v>4.87</v>
+        <v>33.99</v>
       </c>
       <c r="C25" s="98" t="n">
         <v>4.87</v>
@@ -9134,13 +9134,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="88" t="inlineStr">
+      <c r="A26" s="79" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="98" t="n">
-        <v>4.87</v>
+        <v>33.99</v>
       </c>
       <c r="C26" s="98" t="n">
         <v>4.87</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B28" s="98" t="n">
-        <v>-0.9</v>
+        <v>-0.99</v>
       </c>
       <c r="C28" s="98" t="n">
         <v>-0.9</v>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="B29" s="98" t="n">
-        <v>-0.24</v>
+        <v>1.89</v>
       </c>
       <c r="C29" s="98" t="n">
         <v>-0.24</v>
@@ -9582,13 +9582,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="88" t="inlineStr">
+      <c r="A30" s="79" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="98" t="n">
-        <v>7.57</v>
+        <v>25.49</v>
       </c>
       <c r="C30" s="98" t="n">
         <v>7.57</v>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="B31" s="98" t="n">
-        <v>16.82</v>
+        <v>27.77</v>
       </c>
       <c r="C31" s="98" t="n">
         <v>16.82</v>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="B33" s="98" t="n">
-        <v>-0.63</v>
+        <v>0.13</v>
       </c>
       <c r="C33" s="98" t="n">
         <v>-0.63</v>
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="B34" s="98" t="n">
-        <v>1.62</v>
+        <v>4.54</v>
       </c>
       <c r="C34" s="98" t="n">
         <v>1.62</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="B35" s="98" t="n">
-        <v>6.21</v>
+        <v>30.32</v>
       </c>
       <c r="C35" s="98" t="n">
         <v>6.21</v>
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="B36" s="98" t="n">
-        <v>6.21</v>
+        <v>30.32</v>
       </c>
       <c r="C36" s="98" t="n">
         <v>6.21</v>
@@ -10326,168 +10326,168 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B37" s="95" t="inlineStr">
+      <c r="B37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C37" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C37" s="95" t="inlineStr">
+      <c r="D37" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D37" s="95" t="inlineStr">
+      <c r="E37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I37" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E37" s="97" t="inlineStr">
+      <c r="J37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O37" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F37" s="97" t="inlineStr">
+      <c r="Q37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G37" s="97" t="inlineStr">
+      <c r="R37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H37" s="97" t="inlineStr">
+      <c r="S37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O37" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P37" s="97" t="inlineStr">
+      <c r="T37" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U37" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V37" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q37" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R37" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S37" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T37" s="96" t="inlineStr">
+      <c r="X37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U37" s="96" t="inlineStr">
+      <c r="Y37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V37" s="96" t="inlineStr">
+      <c r="Z37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W37" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X37" s="96" t="inlineStr">
+      <c r="AA37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y37" s="96" t="inlineStr">
+      <c r="AB37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z37" s="96" t="inlineStr">
+      <c r="AC37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA37" s="96" t="inlineStr">
+      <c r="AD37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB37" s="96" t="inlineStr">
+      <c r="AE37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="88" t="inlineStr">
+      <c r="A38" s="79" t="inlineStr">
         <is>
           <t>jp225:RNG60</t>
         </is>
       </c>
       <c r="B38" s="98" t="n">
-        <v>-18.71</v>
+        <v>-9.18</v>
       </c>
       <c r="C38" s="98" t="n">
-        <v>-18.71</v>
+        <v>-17.71</v>
       </c>
       <c r="D38" s="98" t="n">
         <v>-5.68</v>
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="B39" s="98" t="n">
-        <v>-15.69</v>
+        <v>-6.02</v>
       </c>
       <c r="C39" s="98" t="n">
-        <v>-15.69</v>
+        <v>-14.66</v>
       </c>
       <c r="D39" s="98" t="n">
         <v>-0.58</v>
@@ -10672,16 +10672,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="88" t="inlineStr">
+      <c r="A40" s="79" t="inlineStr">
         <is>
           <t>jp225:RSI5</t>
         </is>
       </c>
       <c r="B40" s="98" t="n">
-        <v>7.46</v>
+        <v>38.53</v>
       </c>
       <c r="C40" s="98" t="n">
-        <v>7.46</v>
+        <v>7.82</v>
       </c>
       <c r="D40" s="98" t="n">
         <v>17.5</v>
@@ -10769,16 +10769,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="88" t="inlineStr">
+      <c r="A41" s="79" t="inlineStr">
         <is>
           <t>jp225:RSI9</t>
         </is>
       </c>
       <c r="B41" s="98" t="n">
-        <v>12.28</v>
+        <v>35.99</v>
       </c>
       <c r="C41" s="98" t="n">
-        <v>12.28</v>
+        <v>12.75</v>
       </c>
       <c r="D41" s="98" t="n">
         <v>23.03</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="B48" s="98" t="n">
-        <v>8.15</v>
+        <v>8.16</v>
       </c>
       <c r="C48" s="98" t="n">
         <v>8.779999999999999</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="B49" s="98" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="C49" s="98" t="n">
         <v>10.26</v>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="B50" s="98" t="n">
-        <v>24.4</v>
+        <v>24.45</v>
       </c>
       <c r="C50" s="98" t="n">
         <v>25.51</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="B51" s="98" t="n">
-        <v>43.4</v>
+        <v>43.45</v>
       </c>
       <c r="C51" s="98" t="n">
         <v>44.37</v>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="B58" s="98" t="n">
-        <v>-7.49</v>
+        <v>-7.28</v>
       </c>
       <c r="C58" s="98" t="n">
         <v>-7.49</v>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="B59" s="98" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="C59" s="98" t="n">
         <v>2.32</v>
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="B60" s="98" t="n">
-        <v>11.26</v>
+        <v>12.93</v>
       </c>
       <c r="C60" s="98" t="n">
         <v>11.26</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="B61" s="98" t="n">
-        <v>17.31</v>
+        <v>18.4</v>
       </c>
       <c r="C61" s="98" t="n">
         <v>17.31</v>
@@ -13048,7 +13048,7 @@
     <row r="63">
       <c r="A63" s="94" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-12.52&lt;=-10;hk50:RSI6:27.26&lt;=30;us500:RSI2:4.87&lt;=28;us500:RSI2:4.87&lt;=22;us30:RSI3:7.57&lt;=25;ixic:RSI2:6.21&lt;=36;ixic:RSI2:6.21&lt;=35;jp225:RNG60:-18.71&lt;=-10;jp225:RSI5:7.46&lt;=15;jp225:RSI9:12.28&lt;=28;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
+          <t>今日买报：cy:RNG60:-12.52&lt;=-10;hk50:RSI6:27.26&lt;=30;ixic:RSI2:30.32&lt;=36;ixic:RSI2:30.32&lt;=35;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
         </is>
       </c>
     </row>

--- a/report_2408.xlsx
+++ b/report_2408.xlsx
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B25" s="91" t="n">
-        <v>7.19</v>
+        <v>7.17</v>
       </c>
       <c r="C25" s="91" t="n">
         <v>7.16</v>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="B26" s="92" t="n">
-        <v>0.42</v>
+        <v>0.11</v>
       </c>
       <c r="C26" s="92" t="n">
         <v>0.2</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B27" s="92" t="n">
-        <v>-1.39</v>
+        <v>-1.7</v>
       </c>
       <c r="C27" s="92" t="n">
         <v>-1.79</v>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="B23" s="98" t="n">
-        <v>0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="C23" s="98" t="n">
         <v>0.5</v>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="B24" s="98" t="n">
-        <v>5.79</v>
+        <v>3.98</v>
       </c>
       <c r="C24" s="98" t="n">
         <v>5.79</v>
@@ -9037,13 +9037,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="88" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="98" t="n">
-        <v>33.99</v>
+        <v>23.25</v>
       </c>
       <c r="C25" s="98" t="n">
         <v>33.99</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="B26" s="98" t="n">
-        <v>33.99</v>
+        <v>23.25</v>
       </c>
       <c r="C26" s="98" t="n">
         <v>33.99</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B28" s="98" t="n">
-        <v>-0.99</v>
+        <v>-1.9</v>
       </c>
       <c r="C28" s="98" t="n">
         <v>-0.99</v>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="B29" s="98" t="n">
-        <v>1.89</v>
+        <v>0.88</v>
       </c>
       <c r="C29" s="98" t="n">
         <v>1.89</v>
@@ -9582,13 +9582,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="79" t="inlineStr">
+      <c r="A30" s="88" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="98" t="n">
-        <v>25.49</v>
+        <v>20.7</v>
       </c>
       <c r="C30" s="98" t="n">
         <v>25.49</v>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="B31" s="98" t="n">
-        <v>27.77</v>
+        <v>24.56</v>
       </c>
       <c r="C31" s="98" t="n">
         <v>27.77</v>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="B33" s="98" t="n">
-        <v>0.13</v>
+        <v>-0.89</v>
       </c>
       <c r="C33" s="98" t="n">
         <v>0.13</v>
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="B34" s="98" t="n">
-        <v>4.54</v>
+        <v>2.12</v>
       </c>
       <c r="C34" s="98" t="n">
         <v>4.54</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="B35" s="98" t="n">
-        <v>30.32</v>
+        <v>19.85</v>
       </c>
       <c r="C35" s="98" t="n">
         <v>30.32</v>
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="B36" s="98" t="n">
-        <v>30.32</v>
+        <v>19.85</v>
       </c>
       <c r="C36" s="98" t="n">
         <v>30.32</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="B48" s="98" t="n">
-        <v>8.960000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C48" s="98" t="n">
         <v>8.16</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="B49" s="98" t="n">
-        <v>11.57</v>
+        <v>11.81</v>
       </c>
       <c r="C49" s="98" t="n">
         <v>9.77</v>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="B50" s="98" t="n">
-        <v>37.31</v>
+        <v>39.81</v>
       </c>
       <c r="C50" s="98" t="n">
         <v>24.45</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="B51" s="98" t="n">
-        <v>48.26</v>
+        <v>49.32</v>
       </c>
       <c r="C51" s="98" t="n">
         <v>43.45</v>
@@ -12506,9 +12506,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B57" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C57" s="95" t="inlineStr">
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="B58" s="98" t="n">
-        <v>-7.28</v>
+        <v>-6.65</v>
       </c>
       <c r="C58" s="98" t="n">
         <v>-7.28</v>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="B59" s="98" t="n">
-        <v>1.8</v>
+        <v>2.91</v>
       </c>
       <c r="C59" s="98" t="n">
         <v>1.8</v>
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="B60" s="98" t="n">
-        <v>12.93</v>
+        <v>38.96</v>
       </c>
       <c r="C60" s="98" t="n">
         <v>12.93</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="B61" s="98" t="n">
-        <v>18.4</v>
+        <v>35.67</v>
       </c>
       <c r="C61" s="98" t="n">
         <v>18.4</v>
@@ -13048,7 +13048,7 @@
     <row r="63">
       <c r="A63" s="94" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-12.68&lt;=-10;ixic:RSI2:30.32&lt;=36;ixic:RSI2:30.32&lt;=35;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
+          <t>今日买报：cy:RNG60:-12.68&lt;=-10;us500:RSI2:23.25&lt;=28;us30:RSI3:20.7&lt;=25;ixic:RSI2:19.85&lt;=36;ixic:RSI2:19.85&lt;=35;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
         </is>
       </c>
     </row>

--- a/report_2408.xlsx
+++ b/report_2408.xlsx
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B25" s="91" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
       <c r="C25" s="91" t="n">
         <v>7.16</v>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="B26" s="92" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="C26" s="92" t="n">
         <v>0.06</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B27" s="92" t="n">
-        <v>-1.24</v>
+        <v>-1.1</v>
       </c>
       <c r="C27" s="92" t="n">
         <v>-1.74</v>
@@ -8681,9 +8681,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="96" t="inlineStr">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B23" s="98" t="n">
-        <v>-0.44</v>
+        <v>1.87</v>
       </c>
       <c r="C23" s="98" t="n">
         <v>-0.44</v>
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="B24" s="98" t="n">
-        <v>3.98</v>
+        <v>5.76</v>
       </c>
       <c r="C24" s="98" t="n">
         <v>3.98</v>
@@ -9025,13 +9025,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="98" t="n">
-        <v>23.25</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="C25" s="98" t="n">
         <v>23.25</v>
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="B26" s="98" t="n">
-        <v>23.25</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="C26" s="98" t="n">
         <v>23.25</v>
@@ -9224,9 +9224,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B27" s="95" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C27" s="96" t="inlineStr">
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="B28" s="98" t="n">
-        <v>-1.9</v>
+        <v>0.04</v>
       </c>
       <c r="C28" s="98" t="n">
         <v>-1.9</v>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="B29" s="98" t="n">
-        <v>0.88</v>
+        <v>1.74</v>
       </c>
       <c r="C29" s="98" t="n">
         <v>0.88</v>
@@ -9568,13 +9568,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="88" t="inlineStr">
+      <c r="A30" s="79" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="98" t="n">
-        <v>20.7</v>
+        <v>56.47</v>
       </c>
       <c r="C30" s="98" t="n">
         <v>20.7</v>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="B31" s="98" t="n">
-        <v>24.56</v>
+        <v>46.95</v>
       </c>
       <c r="C31" s="98" t="n">
         <v>24.56</v>
@@ -9767,9 +9767,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B32" s="95" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="96" t="inlineStr">
@@ -9923,7 +9923,7 @@
         </is>
       </c>
       <c r="B33" s="98" t="n">
-        <v>-0.89</v>
+        <v>1.66</v>
       </c>
       <c r="C33" s="98" t="n">
         <v>-0.89</v>
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="B34" s="98" t="n">
-        <v>2.12</v>
+        <v>4.74</v>
       </c>
       <c r="C34" s="98" t="n">
         <v>2.12</v>
@@ -10111,13 +10111,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="88" t="inlineStr">
+      <c r="A35" s="79" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="98" t="n">
-        <v>19.85</v>
+        <v>72.11</v>
       </c>
       <c r="C35" s="98" t="n">
         <v>19.85</v>
@@ -10208,13 +10208,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="88" t="inlineStr">
+      <c r="A36" s="79" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="98" t="n">
-        <v>19.85</v>
+        <v>72.11</v>
       </c>
       <c r="C36" s="98" t="n">
         <v>19.85</v>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B48" s="98" t="n">
-        <v>8.029999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="C48" s="98" t="n">
         <v>9.199999999999999</v>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="B49" s="98" t="n">
-        <v>10.37</v>
+        <v>10.25</v>
       </c>
       <c r="C49" s="98" t="n">
         <v>11.81</v>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="B50" s="98" t="n">
-        <v>35.12</v>
+        <v>34.39</v>
       </c>
       <c r="C50" s="98" t="n">
         <v>39.81</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="B51" s="98" t="n">
-        <v>46.44</v>
+        <v>45.95</v>
       </c>
       <c r="C51" s="98" t="n">
         <v>49.32</v>
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="B58" s="98" t="n">
-        <v>-6.65</v>
+        <v>-5.65</v>
       </c>
       <c r="C58" s="98" t="n">
         <v>-6.65</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="B59" s="98" t="n">
-        <v>2.91</v>
+        <v>3.44</v>
       </c>
       <c r="C59" s="98" t="n">
         <v>2.91</v>
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="B60" s="98" t="n">
-        <v>38.96</v>
+        <v>44.49</v>
       </c>
       <c r="C60" s="98" t="n">
         <v>38.96</v>
@@ -12931,7 +12931,7 @@
         </is>
       </c>
       <c r="B61" s="98" t="n">
-        <v>35.67</v>
+        <v>39.51</v>
       </c>
       <c r="C61" s="98" t="n">
         <v>35.67</v>
@@ -13024,7 +13024,7 @@
     <row r="63">
       <c r="A63" s="94" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-12.37&lt;=-10;us500:RSI2:23.25&lt;=28;us30:RSI3:20.7&lt;=25;ixic:RSI2:19.85&lt;=36;ixic:RSI2:19.85&lt;=35;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
+          <t>今日买报：cy:RNG60:-12.37&lt;=-10;fr40:RNG60:-11.77&lt;=-10;fr40:RSI3:16.12&lt;=28</t>
         </is>
       </c>
     </row>
